--- a/slides/linear_regression.xlsx
+++ b/slides/linear_regression.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_cmps460-admin\slides\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_cmps460-content\slides\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393D4A75-1130-4E5E-8FB4-4387E6C4B418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BF36C2-C1D6-49DE-B019-F76E3E185D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{4DB60BD1-2AA0-4BE9-AF0B-E8DCF890EA2E}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>Avg Daily Temp:</t>
   </si>
@@ -135,6 +135,9 @@
   <si>
     <t>Slope: 0.7 &amp; Intercept: 10.87</t>
   </si>
+  <si>
+    <t>Inference</t>
+  </si>
 </sst>
 </file>
 
@@ -143,7 +146,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode=";;;"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,8 +286,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,6 +374,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -495,7 +521,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -578,10 +604,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="7" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -603,6 +629,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4431,16 +4460,16 @@
   </mc:AlternateContent>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>408214</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>9072</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>680357</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>156030</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>36285</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>181429</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>607785</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>143329</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -31752,6 +31781,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:28" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="N1" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
       <c r="X1" s="40" t="s">
         <v>23</v>
       </c>
@@ -32584,7 +32618,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="Z1:AB1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="J2:J3"/>
@@ -32592,6 +32626,7 @@
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="N1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
